--- a/Avance de Proyecto/PMOInformatica Plantilla de Product Backlog.xlsx
+++ b/Avance de Proyecto/PMOInformatica Plantilla de Product Backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmeji\Desktop\MASTER\Universidad\9no Semestre\Comunicacion de Datos\ProyIntComDat25B_3.1416chul-s\ProyIntComDat25B_3.1416chul-s\Avance de Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3086C7D-FA07-41B5-8FC7-BDFDFB023F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BB0DBB-4BBB-4EC1-81C6-8C73F1E61D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="189">
   <si>
     <t>Columna</t>
   </si>
@@ -360,6 +360,246 @@
   </si>
   <si>
     <t>En proceso</t>
+  </si>
+  <si>
+    <t>HU-2025-021</t>
+  </si>
+  <si>
+    <t>HU-2025-022</t>
+  </si>
+  <si>
+    <t>HU-2025-023</t>
+  </si>
+  <si>
+    <t>HU-2025-024</t>
+  </si>
+  <si>
+    <t>HU-2025-025</t>
+  </si>
+  <si>
+    <t>HU-2025-026</t>
+  </si>
+  <si>
+    <t>HU-2025-027</t>
+  </si>
+  <si>
+    <t>HU-2025-028</t>
+  </si>
+  <si>
+    <t>HU-2025-029</t>
+  </si>
+  <si>
+    <t>HU-2025-030</t>
+  </si>
+  <si>
+    <t>HU-2025-031</t>
+  </si>
+  <si>
+    <t>HU-2025-032</t>
+  </si>
+  <si>
+    <t>HU-2025-033</t>
+  </si>
+  <si>
+    <t>HU-2025-034</t>
+  </si>
+  <si>
+    <t>HU-2025-035</t>
+  </si>
+  <si>
+    <t>HU-2025-036</t>
+  </si>
+  <si>
+    <t>HU-2025-037</t>
+  </si>
+  <si>
+    <t>HU-2025-038</t>
+  </si>
+  <si>
+    <t>HU-2025-039</t>
+  </si>
+  <si>
+    <t>HU-2025-040</t>
+  </si>
+  <si>
+    <t>Como estudiante, necesito acceder a una guía interactiva en línea para entender mejor el proceso de inscripción, con la finalidad de reducir errores al registrarme.</t>
+  </si>
+  <si>
+    <t>Como docente, necesito descargar guías en formato accesible (PDF) para facilitar su uso offline, con la finalidad de consultarlas sin conexión.</t>
+  </si>
+  <si>
+    <t>Como administrador, necesito recibir notificaciones automáticas cuando un estudiante completa una encuesta, con la finalidad de monitorear participación.</t>
+  </si>
+  <si>
+    <t>Como coordinador, necesito consultar estadísticas de visualización de videos, con la finalidad de evaluar la efectividad de los materiales.</t>
+  </si>
+  <si>
+    <t>Como estudiante, necesito recibir una confirmación automática al enviar encuestas, con la finalidad de tener certeza de que mi opinión fue registrada.</t>
+  </si>
+  <si>
+    <t>Como docente, necesito visualizar una galería centralizada de guías y videos, con la finalidad de consultarlos por tema o área.</t>
+  </si>
+  <si>
+    <t>Como equipo de soporte, necesito actualizar versiones anteriores de guías sin perder el historial, con la finalidad de mantener control de versiones.</t>
+  </si>
+  <si>
+    <t>Como coordinador, necesito recibir un reporte mensual automatizado, con la finalidad de supervisar el progreso y cumplimiento del proyecto.</t>
+  </si>
+  <si>
+    <t>Como estudiante, necesito valorar la claridad de las guías mediante estrellas o calificación, con la finalidad de mejorar los materiales.</t>
+  </si>
+  <si>
+    <t>Como administrador, necesito controlar permisos de acceso a las guías, con la finalidad de asegurar que sólo usuarios autorizados las editen.</t>
+  </si>
+  <si>
+    <t>Como diseñador, necesito crear una plantilla para miniaturas de video, con la finalidad de mantener coherencia visual.</t>
+  </si>
+  <si>
+    <t>Como alumno nuevo, necesito un video introductorio sobre el uso del portal institucional, con la finalidad de orientarme rápidamente.</t>
+  </si>
+  <si>
+    <t>Como docente, necesito una guía sobre cómo registrar calificaciones en línea, con la finalidad de reducir errores en el sistema.</t>
+  </si>
+  <si>
+    <t>Como responsable de becas, necesito una guía audiovisual para nuevos beneficiarios, con la finalidad de agilizar el registro de becas.</t>
+  </si>
+  <si>
+    <t>Como equipo del proyecto, necesito una plantilla estándar para encuestas de satisfacción, con la finalidad de mantener uniformidad.</t>
+  </si>
+  <si>
+    <t>Como coordinador académico, necesito que el sistema genere alertas cuando haya guías desactualizadas, con la finalidad de mantener materiales vigentes.</t>
+  </si>
+  <si>
+    <t>Como estudiante, necesito un acceso rápido desde Teams a las guías, con la finalidad de consultarlas sin salir de la clase.</t>
+  </si>
+  <si>
+    <t>Como administrador, necesito almacenar respaldos automáticos de las guías, con la finalidad de evitar pérdida de información.</t>
+  </si>
+  <si>
+    <t>Como equipo de comunicación, necesito difundir los resultados del proyecto mediante boletines digitales, con la finalidad de dar visibilidad institucional.</t>
+  </si>
+  <si>
+    <t>Como gerente del proyecto, necesito un dashboard final con métricas clave, con la finalidad de evaluar el impacto del proyecto.</t>
+  </si>
+  <si>
+    <t>Guía interactiva de inscripción</t>
+  </si>
+  <si>
+    <t>Guías descargables</t>
+  </si>
+  <si>
+    <t>Notificaciones automáticas</t>
+  </si>
+  <si>
+    <t>Confirmación de encuesta</t>
+  </si>
+  <si>
+    <t>Biblioteca digital</t>
+  </si>
+  <si>
+    <t>Control de versiones</t>
+  </si>
+  <si>
+    <t>Reporte automatizado</t>
+  </si>
+  <si>
+    <t>Sistema de valoración</t>
+  </si>
+  <si>
+    <t>Gestión de permisos</t>
+  </si>
+  <si>
+    <t>Miniaturas institucionales</t>
+  </si>
+  <si>
+    <t>Video introductorio</t>
+  </si>
+  <si>
+    <t>Guía registro de calificaciones</t>
+  </si>
+  <si>
+    <t>Video becas institucionales</t>
+  </si>
+  <si>
+    <t>Plantilla de encuestas</t>
+  </si>
+  <si>
+    <t>Alertas de actualización</t>
+  </si>
+  <si>
+    <t>Integración Teams</t>
+  </si>
+  <si>
+    <t>Copias de seguridad</t>
+  </si>
+  <si>
+    <t>Dashboard de resultados</t>
+  </si>
+  <si>
+    <t>Boletín institucional</t>
+  </si>
+  <si>
+    <t>Métricas de visualización</t>
+  </si>
+  <si>
+    <t>Se vincula con materiales multimedia y QR existentes.</t>
+  </si>
+  <si>
+    <t>Considerar accesibilidad y legibilidad en móviles</t>
+  </si>
+  <si>
+    <t>Requiere integración con API de Forms o correo institucional.</t>
+  </si>
+  <si>
+    <t>Puede usarse API de YouTube o Moodle Analytics</t>
+  </si>
+  <si>
+    <t>Integra API de Google Forms o Microsoft Forms.</t>
+  </si>
+  <si>
+    <t>Publicación mediante SharePoint o Teams.</t>
+  </si>
+  <si>
+    <t>Uso de repositorio interno o control documental.</t>
+  </si>
+  <si>
+    <t>Generado en Excel o Power BI conectado a formularios.</t>
+  </si>
+  <si>
+    <t>Puede usarse un formulario o plugin evaluativo.</t>
+  </si>
+  <si>
+    <t>Vinculado con políticas institucionales.</t>
+  </si>
+  <si>
+    <t>Uso de Canva, Figma o PowerPoint.</t>
+  </si>
+  <si>
+    <t>Puede incluir subtítulos e íconos institucionales.</t>
+  </si>
+  <si>
+    <t>Complementa la historia HU-002.</t>
+  </si>
+  <si>
+    <t>Vinculada con HU-004 y HU-011.</t>
+  </si>
+  <si>
+    <t>Basada en Forms o Google Forms.</t>
+  </si>
+  <si>
+    <t>Integración con metadatos de publicación.</t>
+  </si>
+  <si>
+    <t>Puede implementarse con la API de Microsoft Graph.</t>
+  </si>
+  <si>
+    <t>Copias automáticas en OneDrive o SharePoint.</t>
+  </si>
+  <si>
+    <t>Se publica en las redes institucionales.</t>
+  </si>
+  <si>
+    <t>Se crea en Power BI con datos del sistema.</t>
   </si>
 </sst>
 </file>
@@ -785,18 +1025,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I25"/>
+  <dimension ref="B1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="88.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="157.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="43.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.140625" style="2" customWidth="1"/>
     <col min="11" max="16384" width="11.42578125" style="2"/>
   </cols>
@@ -837,7 +1077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:9" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
         <v>21</v>
       </c>
@@ -1359,6 +1599,526 @@
     </row>
     <row r="25" spans="2:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C25" s="11"/>
+    </row>
+    <row r="26" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="8">
+        <v>5</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="8">
+        <v>5</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="8">
+        <v>5</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="8">
+        <v>3</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="8">
+        <v>5</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F32" s="8">
+        <v>4</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="8">
+        <v>4</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" s="8">
+        <v>4</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" s="9" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="8">
+        <v>4</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="8">
+        <v>5</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="8">
+        <v>4</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="8">
+        <v>5</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="8">
+        <v>3</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="8">
+        <v>4</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="8">
+        <v>5</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="8">
+        <v>4</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="8">
+        <v>4</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="9" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="8">
+        <v>5</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>188</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
